--- a/excle活頁簿應用文件/CC2站_V2_0VAh_20268_電容範圍_0.00_200000.00_加總計算.xlsx
+++ b/excle活頁簿應用文件/CC2站_V2_0VAh_20268_電容範圍_0.00_200000.00_加總計算.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30416"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bh205\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bh205\OneDrive\文件\工作常用指令及計畫\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABB66AD-15F0-4724-8530-9236FD5520A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E6C4DC9-4719-4038-8BE1-C211F2D523D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1290,7 +1290,7 @@
         <v>have</v>
       </c>
       <c r="H2">
-        <f>COUNTIFS($G:$G,"have")</f>
+        <f>COUNTIFS($G:$G,"have",$G:$G,"&lt;&gt;")</f>
         <v>176</v>
       </c>
       <c r="I2">
